--- a/artfynd/A 23929-2025 artfynd.xlsx
+++ b/artfynd/A 23929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135017087</v>
+        <v>137568657</v>
       </c>
       <c r="B3" t="n">
-        <v>83289</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613699</v>
+        <v>613823</v>
       </c>
       <c r="R3" t="n">
-        <v>7256643</v>
+        <v>7256433</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,74 +878,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre, lövrik barrblandskog på blåbärsris med inslag av senvuxna granar</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017087</t>
+          <t>https://artportalen.se/Sighting/137568657</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135017099</v>
+        <v>137568658</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613793</v>
+        <v>613787</v>
       </c>
       <c r="R4" t="n">
-        <v>7256414</v>
+        <v>7256389</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,12 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,36 +994,35 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Frisk, äldre barrblandskog på blåbärsris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017099</t>
+          <t>https://artportalen.se/Sighting/137568658</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135017092</v>
+        <v>137568660</v>
       </c>
       <c r="B5" t="n">
-        <v>83425</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,37 +1030,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613817</v>
+        <v>613785</v>
       </c>
       <c r="R5" t="n">
-        <v>7256514</v>
+        <v>7256381</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,27 +1110,1185 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Frisk, äldre barrblandskog med inslag av mycket gamla, senvuxna granar</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135017087</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83289</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613699</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7256643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre, lövrik barrblandskog på blåbärsris med inslag av senvuxna granar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017087</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137568655</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83407</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>613861</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7256531</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568655</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135017099</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79438</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>613793</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7256414</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Frisk, äldre barrblandskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017099</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137568671</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>613730</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7256672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>74</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568671</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135017092</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83425</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjoubbamyran-Södra Drappotjärnen, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>613817</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7256514</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Frisk, äldre barrblandskog med inslag av mycket gamla, senvuxna granar</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135017092</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137568665</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>613762</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7256435</v>
+      </c>
+      <c r="S11" t="n">
+        <v>18</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skalad klen gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568665</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137568669</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>613713</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7256640</v>
+      </c>
+      <c r="S12" t="n">
+        <v>35</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skalad klen gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568669</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137568667</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57215</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>613759</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7256524</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568667</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137568666</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>613787</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7256493</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568666</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137568673</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58199</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>skogsmonitor Fräkenmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>613876</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7256595</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568673</t>
         </is>
       </c>
     </row>
@@ -1112,6 +2298,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
